--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.10147059178034</v>
+        <v>5.703988971164305</v>
       </c>
       <c r="D2" t="n">
-        <v>33.71697181844802</v>
+        <v>5.479007920497804</v>
       </c>
       <c r="E2" t="n">
-        <v>22.62988207853677</v>
+        <v>3.677355837762226</v>
       </c>
       <c r="F2" t="n">
-        <v>11.12746826544452</v>
+        <v>1.808213593134735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.6369426890251</v>
+        <v>6.603503186966579</v>
       </c>
       <c r="D3" t="n">
-        <v>41.22349737845044</v>
+        <v>6.698818323998196</v>
       </c>
       <c r="E3" t="n">
-        <v>22.62988207853677</v>
+        <v>3.677355837762226</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12746826544452</v>
+        <v>1.808213593134735</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.56108042546247</v>
+        <v>1.716175569137651</v>
       </c>
       <c r="D4" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="E4" t="n">
-        <v>22.62988207853677</v>
+        <v>3.677355837762226</v>
       </c>
       <c r="F4" t="n">
-        <v>11.12746826544452</v>
+        <v>1.808213593134735</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>80.59569203754299</v>
+        <v>13.09679995610074</v>
       </c>
       <c r="D5" t="n">
-        <v>38.97168255355241</v>
+        <v>6.332898414952266</v>
       </c>
       <c r="E5" t="n">
-        <v>22.62988207853677</v>
+        <v>3.677355837762226</v>
       </c>
       <c r="F5" t="n">
-        <v>11.12746826544452</v>
+        <v>1.808213593134735</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.26409182027978</v>
+        <v>5.730414920795464</v>
       </c>
       <c r="D6" t="n">
-        <v>35.45620825071261</v>
+        <v>5.761633840740799</v>
       </c>
       <c r="E6" t="n">
-        <v>22.62988207853677</v>
+        <v>3.677355837762226</v>
       </c>
       <c r="F6" t="n">
-        <v>11.12746826544452</v>
+        <v>1.808213593134735</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
